--- a/Tableau_Synthese_E5_Enzo.xlsx
+++ b/Tableau_Synthese_E5_Enzo.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Vmav9vei6bKMKY7msxJSXnW0IjorklatzkrN8kKggmk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="MNHW0PTEyfINZpzMmnFbLVwOP6/03tBk7R77TIQ6tVI="/>
     </ext>
   </extLst>
 </workbook>
@@ -30,7 +30,7 @@
     <t>NOM et prénom : GOUPIL Enzo</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
+    <t>N° candidat : 02541519342</t>
   </si>
   <si>
     <t>Centre de formation : Caen supp Saint-Ursule</t>
@@ -49,7 +49,9 @@
       <rPr>
         <rFont val="Arial"/>
         <b/>
+        <color rgb="FF0000FF"/>
         <sz val="18.0"/>
+        <u/>
       </rPr>
       <t xml:space="preserve">Adresse URL du portfolio : </t>
     </r>
@@ -61,7 +63,7 @@
         <sz val="18.0"/>
         <u/>
       </rPr>
-      <t>https://enzo-gpl.github.io/Portfolio-V8/</t>
+      <t>https://enzo-gpl.github.io/Portfolio-sisr/</t>
     </r>
   </si>
   <si>
@@ -268,7 +270,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="25">
     <border/>
     <border>
       <left style="medium">
@@ -537,53 +539,11 @@
         <color rgb="FF494429"/>
       </bottom>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -591,19 +551,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -611,7 +571,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -636,22 +596,19 @@
     <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" textRotation="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="22" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="23" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="23" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -659,31 +616,13 @@
     <xf borderId="24" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="23" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1020,7 +959,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" ht="12.75" customHeight="1">
+    <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="25" t="s">
         <v>24</v>
       </c>
@@ -1032,7 +971,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" ht="39.75" customHeight="1">
+    <row r="9" ht="32.25" customHeight="1">
       <c r="A9" s="26" t="s">
         <v>25</v>
       </c>
@@ -1042,15 +981,15 @@
       <c r="C9" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="28" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="30"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" ht="39.75" customHeight="1">
       <c r="A10" s="26" t="s">
@@ -1062,13 +1001,13 @@
       <c r="C10" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
       <c r="G10" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="30"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" ht="39.75" customHeight="1">
       <c r="A11" s="26" t="s">
@@ -1077,12 +1016,12 @@
       <c r="B11" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="31" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1096,301 +1035,301 @@
       <c r="C12" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="29"/>
+      <c r="D12" s="28"/>
       <c r="E12" s="28"/>
       <c r="F12" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="31" t="s">
+      <c r="G12" s="28"/>
+      <c r="H12" s="29" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" ht="39.75" customHeight="1">
       <c r="A13" s="26"/>
-      <c r="B13" s="32"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="28"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="31"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" ht="39.75" customHeight="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="30"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" ht="39.75" customHeight="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="30"/>
-    </row>
-    <row r="16" ht="39.75" customHeight="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="30"/>
-    </row>
-    <row r="17" ht="39.75" customHeight="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="30"/>
-    </row>
-    <row r="18" ht="39.75" customHeight="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="30"/>
-    </row>
-    <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="34" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
+    </row>
+    <row r="16" ht="17.25" customHeight="1">
+      <c r="A16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="35"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="32"/>
+    </row>
+    <row r="17" ht="39.75" customHeight="1">
+      <c r="A17" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
+    </row>
+    <row r="18" ht="39.75" customHeight="1">
+      <c r="A18" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" ht="39.75" customHeight="1">
+      <c r="A19" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" ht="39.75" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B20" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="28" t="s">
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="30"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" ht="39.75" customHeight="1">
-      <c r="A21" s="26" t="s">
-        <v>35</v>
+      <c r="A21" s="26"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
+    </row>
+    <row r="22" ht="39.75" customHeight="1">
+      <c r="A22" s="26"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29"/>
+    </row>
+    <row r="23" ht="21.0" customHeight="1">
+      <c r="A23" s="31" t="s">
+        <v>38</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>34</v>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="32"/>
+    </row>
+    <row r="24" ht="39.75" customHeight="1">
+      <c r="A24" s="26" t="s">
+        <v>39</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="B24" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="E24" s="28"/>
+      <c r="F24" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="28" t="s">
+      <c r="G24" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H21" s="30"/>
-    </row>
-    <row r="22" ht="39.75" customHeight="1">
-      <c r="A22" s="26" t="s">
-        <v>36</v>
+      <c r="H24" s="29"/>
+    </row>
+    <row r="25" ht="39.75" customHeight="1">
+      <c r="A25" s="26" t="s">
+        <v>41</v>
       </c>
-      <c r="B22" s="27" t="s">
-        <v>34</v>
+      <c r="B25" s="27" t="s">
+        <v>40</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="28" t="s">
+      <c r="C25" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="28" t="s">
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="29"/>
+    </row>
+    <row r="26" ht="39.75" customHeight="1">
+      <c r="A26" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="30"/>
-    </row>
-    <row r="23" ht="39.75" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="30"/>
-    </row>
-    <row r="24" ht="39.75" customHeight="1">
-      <c r="A24" s="33"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="30"/>
-    </row>
-    <row r="25" ht="39.75" customHeight="1">
-      <c r="A25" s="33"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="30"/>
-    </row>
-    <row r="26" ht="39.75" customHeight="1">
-      <c r="A26" s="33"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="30"/>
-    </row>
-    <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="35"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
+    </row>
+    <row r="27" ht="39.75" customHeight="1">
+      <c r="A27" s="26"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="29"/>
     </row>
     <row r="28" ht="39.75" customHeight="1">
-      <c r="A28" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="28" t="s">
-        <v>27</v>
-      </c>
+      <c r="A28" s="26"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
       <c r="E28" s="28"/>
-      <c r="F28" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="30"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="29"/>
     </row>
     <row r="29" ht="39.75" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>27</v>
-      </c>
+      <c r="A29" s="26"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="28"/>
       <c r="D29" s="28"/>
-      <c r="E29" s="29"/>
+      <c r="E29" s="28"/>
       <c r="F29" s="28"/>
       <c r="G29" s="28"/>
-      <c r="H29" s="30"/>
-    </row>
-    <row r="30" ht="39.75" customHeight="1">
-      <c r="A30" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="30"/>
-    </row>
-    <row r="31" ht="39.75" customHeight="1">
-      <c r="A31" s="33"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="30"/>
-    </row>
-    <row r="32" ht="39.75" customHeight="1">
-      <c r="A32" s="33"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="30"/>
-    </row>
-    <row r="33" ht="39.75" customHeight="1">
-      <c r="A33" s="33"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="30"/>
-    </row>
-    <row r="34" ht="39.75" customHeight="1">
-      <c r="A34" s="36"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
+      <c r="H29" s="29"/>
+    </row>
+    <row r="30" ht="12.75" customHeight="1">
+      <c r="A30" s="33"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+    </row>
+    <row r="31" ht="12.75" customHeight="1">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" ht="12.75" customHeight="1">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" ht="12.75" customHeight="1">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" ht="12.75" customHeight="1">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="40"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="7"/>
@@ -10992,63 +10931,13 @@
       <c r="G995" s="7"/>
       <c r="H995" s="7"/>
     </row>
-    <row r="996" ht="12.75" customHeight="1">
-      <c r="A996" s="7"/>
-      <c r="B996" s="7"/>
-      <c r="C996" s="7"/>
-      <c r="D996" s="7"/>
-      <c r="E996" s="7"/>
-      <c r="F996" s="7"/>
-      <c r="G996" s="7"/>
-      <c r="H996" s="7"/>
-    </row>
-    <row r="997" ht="12.75" customHeight="1">
-      <c r="A997" s="7"/>
-      <c r="B997" s="7"/>
-      <c r="C997" s="7"/>
-      <c r="D997" s="7"/>
-      <c r="E997" s="7"/>
-      <c r="F997" s="7"/>
-      <c r="G997" s="7"/>
-      <c r="H997" s="7"/>
-    </row>
-    <row r="998" ht="12.75" customHeight="1">
-      <c r="A998" s="7"/>
-      <c r="B998" s="7"/>
-      <c r="C998" s="7"/>
-      <c r="D998" s="7"/>
-      <c r="E998" s="7"/>
-      <c r="F998" s="7"/>
-      <c r="G998" s="7"/>
-      <c r="H998" s="7"/>
-    </row>
-    <row r="999" ht="12.75" customHeight="1">
-      <c r="A999" s="7"/>
-      <c r="B999" s="7"/>
-      <c r="C999" s="7"/>
-      <c r="D999" s="7"/>
-      <c r="E999" s="7"/>
-      <c r="F999" s="7"/>
-      <c r="G999" s="7"/>
-      <c r="H999" s="7"/>
-    </row>
-    <row r="1000" ht="12.75" customHeight="1">
-      <c r="A1000" s="7"/>
-      <c r="B1000" s="7"/>
-      <c r="C1000" s="7"/>
-      <c r="D1000" s="7"/>
-      <c r="E1000" s="7"/>
-      <c r="F1000" s="7"/>
-      <c r="G1000" s="7"/>
-      <c r="H1000" s="7"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A2:H2"/>
